--- a/03_GD32F407_FreeRTOS_BinarySemaphore/Project/GD32F407_analysis.xlsx
+++ b/03_GD32F407_FreeRTOS_BinarySemaphore/Project/GD32F407_analysis.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="42">
   <si>
     <t>GD32F407</t>
   </si>
@@ -78,9 +78,6 @@
   </si>
   <si>
     <t>list.o</t>
-  </si>
-  <si>
-    <t>systick.o</t>
   </si>
   <si>
     <t>init.o</t>
@@ -233,9 +230,9 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>ram_percent!$A$3:$A$35</c:f>
+              <c:f>ram_percent!$A$3:$A$34</c:f>
               <c:strCache>
-                <c:ptCount val="33"/>
+                <c:ptCount val="32"/>
                 <c:pt idx="0">
                   <c:v>heap_4.o</c:v>
                 </c:pt>
@@ -272,7 +269,7 @@
                 <c:pt idx="11">
                   <c:v>bsp_keys.o</c:v>
                 </c:pt>
-                <c:pt idx="32">
+                <c:pt idx="31">
                   <c:v>Totals</c:v>
                 </c:pt>
               </c:strCache>
@@ -280,47 +277,47 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>ram_percent!$B$3:$B$35</c:f>
+              <c:f>ram_percent!$B$3:$B$34</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="33"/>
+                <c:ptCount val="32"/>
                 <c:pt idx="0">
-                  <c:v>96.2117919921875</c:v>
+                  <c:v>96.22624969482422</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.287365555763245</c:v>
+                  <c:v>1.287559032440186</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.282356381416321</c:v>
+                  <c:v>1.282549023628235</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.001840829849243</c:v>
+                  <c:v>1.001991510391235</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.08014727383852005</c:v>
+                  <c:v>0.08015931397676468</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.07513806968927383</c:v>
+                  <c:v>0.07514935731887817</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.03005522675812244</c:v>
+                  <c:v>0.01502987183630467</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.01127071026712656</c:v>
+                  <c:v>0.01127240434288979</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.005009204614907503</c:v>
+                  <c:v>0.005009957123547792</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.005009204614907503</c:v>
+                  <c:v>0.005009957123547792</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.005009204614907503</c:v>
+                  <c:v>0.005009957123547792</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.005009204614907503</c:v>
-                </c:pt>
-                <c:pt idx="32">
+                  <c:v>0.005009957123547792</c:v>
+                </c:pt>
+                <c:pt idx="31">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -388,9 +385,9 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>flash_percent!$A$3:$A$35</c:f>
+              <c:f>flash_percent!$A$3:$A$34</c:f>
               <c:strCache>
-                <c:ptCount val="33"/>
+                <c:ptCount val="32"/>
                 <c:pt idx="0">
                   <c:v>tasks.o</c:v>
                 </c:pt>
@@ -404,34 +401,34 @@
                   <c:v>port.o</c:v>
                 </c:pt>
                 <c:pt idx="4">
+                  <c:v>mc_w.l</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>heap_4.o</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>gd32f4xx_usart.o</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>usart0.o</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>system_gd32f4xx.o</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>printf3.o</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>exti.o</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>gd32f4xx_dma.o</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>startup_gd32f407_427.o</c:v>
+                </c:pt>
+                <c:pt idx="13">
                   <c:v>main.o</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>mc_w.l</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>heap_4.o</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>gd32f4xx_usart.o</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>usart0.o</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>system_gd32f4xx.o</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>printf3.o</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>exti.o</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>gd32f4xx_dma.o</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>startup_gd32f407_427.o</c:v>
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>gd32f4xx_rcu.o</c:v>
@@ -449,45 +446,42 @@
                   <c:v>list.o</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>systick.o</c:v>
+                  <c:v>init.o</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>init.o</c:v>
+                  <c:v>uidiv.o</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>uidiv.o</c:v>
+                  <c:v>puts.o</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>puts.o</c:v>
+                  <c:v>memseta.o</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>memseta.o</c:v>
+                  <c:v>memcpya.o</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>memcpya.o</c:v>
+                  <c:v>handlers.o</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>handlers.o</c:v>
+                  <c:v>gd32f4xx_exti.o</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>gd32f4xx_exti.o</c:v>
+                  <c:v>gd32f4xx_it.o</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>gd32f4xx_it.o</c:v>
+                  <c:v>entry9a.o</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>entry9a.o</c:v>
+                  <c:v>entry2.o</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>entry2.o</c:v>
+                  <c:v>stdout.o</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>stdout.o</c:v>
+                  <c:v>entry5.o</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>entry5.o</c:v>
-                </c:pt>
-                <c:pt idx="32">
                   <c:v>Totals</c:v>
                 </c:pt>
               </c:strCache>
@@ -495,107 +489,104 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>flash_percent!$B$3:$B$35</c:f>
+              <c:f>flash_percent!$B$3:$B$34</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="33"/>
+                <c:ptCount val="32"/>
                 <c:pt idx="0">
-                  <c:v>22.00537872314453</c:v>
+                  <c:v>24.98612403869629</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>13.32321929931641</c:v>
+                  <c:v>8.104036331176758</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>8.337355613708496</c:v>
+                  <c:v>7.44588041305542</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>7.12364673614502</c:v>
+                  <c:v>7.271429538726807</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5.047927856445313</c:v>
+                  <c:v>5.756878852844238</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>5.006551265716553</c:v>
+                  <c:v>5.265244483947754</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>4.578994750976563</c:v>
+                  <c:v>4.694314479827881</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>4.08247709274292</c:v>
+                  <c:v>4.472286224365234</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3.889386892318726</c:v>
+                  <c:v>4.234398365020752</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>3.682504653930664</c:v>
+                  <c:v>3.742764234542847</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>3.254947900772095</c:v>
+                  <c:v>3.726905107498169</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>3.241155862808228</c:v>
+                  <c:v>3.441440105438232</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2.992897033691406</c:v>
+                  <c:v>3.39386248588562</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2.951520681381226</c:v>
+                  <c:v>2.410593986511231</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.986069917678833</c:v>
+                  <c:v>2.28372049331665</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>1.889524817466736</c:v>
+                  <c:v>2.172706365585327</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.627473950386047</c:v>
+                  <c:v>1.63349461555481</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.241293668746948</c:v>
+                  <c:v>1.427325367927551</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1.034411430358887</c:v>
+                  <c:v>1.189437747001648</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.6620233058929443</c:v>
+                  <c:v>0.3806200921535492</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.3310116529464722</c:v>
+                  <c:v>0.3489017486572266</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.3034273386001587</c:v>
+                  <c:v>0.2854650616645813</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.2482587397098541</c:v>
+                  <c:v>0.2854650616645813</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.2482587397098541</c:v>
+                  <c:v>0.2854650616645813</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.2482587397098541</c:v>
+                  <c:v>0.2378875613212585</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.2068822830915451</c:v>
+                  <c:v>0.2378875613212585</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.2068822830915451</c:v>
+                  <c:v>0.0951550230383873</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.08275291323661804</c:v>
+                  <c:v>0.06343667954206467</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.05516861006617546</c:v>
+                  <c:v>0.06343667954206467</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.05516861006617546</c:v>
+                  <c:v>0.03171833977103233</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.02758430503308773</c:v>
+                  <c:v>0.03171833977103233</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.02758430503308773</c:v>
-                </c:pt>
-                <c:pt idx="32">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -700,8 +691,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A2:H35" totalsRowCount="1">
-  <autoFilter ref="A2:H34"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A2:H34" totalsRowCount="1">
+  <autoFilter ref="A2:H33"/>
   <tableColumns count="8">
     <tableColumn id="1" name="File_name" totalsRowLabel="Totals"/>
     <tableColumn id="2" name="ram_percent" totalsRowFunction="sum"/>
@@ -717,8 +708,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A2:H35" totalsRowCount="1">
-  <autoFilter ref="A2:H34"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A2:H34" totalsRowCount="1">
+  <autoFilter ref="A2:H33"/>
   <tableColumns count="8">
     <tableColumn id="1" name="File_name" totalsRowLabel="Totals"/>
     <tableColumn id="2" name="flash_percent" totalsRowFunction="sum"/>
@@ -1018,7 +1009,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H35"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="16.7109375" customWidth="1"/>
@@ -1031,28 +1022,28 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2" t="s">
         <v>35</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>36</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>37</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>38</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>39</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>40</v>
-      </c>
-      <c r="H2" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1060,7 +1051,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>96.2117919921875</v>
+        <v>96.22624969482422</v>
       </c>
       <c r="C3" s="1">
         <v>76828</v>
@@ -1086,7 +1077,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="2">
-        <v>1.287365555763245</v>
+        <v>1.287559032440186</v>
       </c>
       <c r="C4" s="1">
         <v>1028</v>
@@ -1112,7 +1103,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="2">
-        <v>1.282356381416321</v>
+        <v>1.282549023628235</v>
       </c>
       <c r="C5" s="1">
         <v>1024</v>
@@ -1138,16 +1129,16 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>1.001840829849243</v>
+        <v>1.001991510391235</v>
       </c>
       <c r="C6" s="1">
         <v>800</v>
       </c>
       <c r="D6" s="1">
-        <v>3191</v>
+        <v>3151</v>
       </c>
       <c r="E6" s="1">
-        <v>3148</v>
+        <v>3108</v>
       </c>
       <c r="F6" s="1">
         <v>43</v>
@@ -1164,16 +1155,16 @@
         <v>5</v>
       </c>
       <c r="B7" s="2">
-        <v>0.08014727383852005</v>
+        <v>0.08015931397676468</v>
       </c>
       <c r="C7" s="1">
         <v>64</v>
       </c>
       <c r="D7" s="1">
-        <v>1932</v>
+        <v>1022</v>
       </c>
       <c r="E7" s="1">
-        <v>1912</v>
+        <v>1002</v>
       </c>
       <c r="F7" s="1">
         <v>20</v>
@@ -1190,16 +1181,16 @@
         <v>6</v>
       </c>
       <c r="B8" s="2">
-        <v>0.07513806968927383</v>
+        <v>0.07514935731887817</v>
       </c>
       <c r="C8" s="1">
         <v>60</v>
       </c>
       <c r="D8" s="1">
-        <v>1209</v>
+        <v>939</v>
       </c>
       <c r="E8" s="1">
-        <v>1188</v>
+        <v>918</v>
       </c>
       <c r="F8" s="1">
         <v>21</v>
@@ -1216,16 +1207,16 @@
         <v>7</v>
       </c>
       <c r="B9" s="2">
-        <v>0.03005522675812244</v>
+        <v>0.01502987183630467</v>
       </c>
       <c r="C9" s="1">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="D9" s="1">
-        <v>732</v>
+        <v>304</v>
       </c>
       <c r="E9" s="1">
-        <v>732</v>
+        <v>304</v>
       </c>
       <c r="F9" s="1">
         <v>0</v>
@@ -1234,7 +1225,7 @@
         <v>0</v>
       </c>
       <c r="H9" s="1">
-        <v>24</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1242,16 +1233,16 @@
         <v>8</v>
       </c>
       <c r="B10" s="2">
-        <v>0.01127071026712656</v>
+        <v>0.01127240434288979</v>
       </c>
       <c r="C10" s="1">
         <v>9</v>
       </c>
       <c r="D10" s="1">
-        <v>1033</v>
+        <v>917</v>
       </c>
       <c r="E10" s="1">
-        <v>988</v>
+        <v>872</v>
       </c>
       <c r="F10" s="1">
         <v>41</v>
@@ -1268,7 +1259,7 @@
         <v>9</v>
       </c>
       <c r="B11" s="2">
-        <v>0.005009204614907503</v>
+        <v>0.005009957123547792</v>
       </c>
       <c r="C11" s="1">
         <v>4</v>
@@ -1294,7 +1285,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="2">
-        <v>0.005009204614907503</v>
+        <v>0.005009957123547792</v>
       </c>
       <c r="C12" s="1">
         <v>4</v>
@@ -1320,7 +1311,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="2">
-        <v>0.005009204614907503</v>
+        <v>0.005009957123547792</v>
       </c>
       <c r="C13" s="1">
         <v>4</v>
@@ -1346,16 +1337,16 @@
         <v>12</v>
       </c>
       <c r="B14" s="2">
-        <v>0.005009204614907503</v>
+        <v>0.005009957123547792</v>
       </c>
       <c r="C14" s="1">
         <v>4</v>
       </c>
       <c r="D14" s="1">
-        <v>236</v>
+        <v>206</v>
       </c>
       <c r="E14" s="1">
-        <v>232</v>
+        <v>202</v>
       </c>
       <c r="F14" s="1">
         <v>0</v>
@@ -1367,35 +1358,35 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:8">
-      <c r="A35" t="s">
-        <v>34</v>
-      </c>
-      <c r="B35">
+    <row r="34" spans="1:8">
+      <c r="A34" t="s">
+        <v>33</v>
+      </c>
+      <c r="B34">
         <f>SUBTOTAL(109,[ram_percent])</f>
         <v>0</v>
       </c>
-      <c r="C35">
+      <c r="C34">
         <f>SUBTOTAL(109,[ram])</f>
         <v>0</v>
       </c>
-      <c r="D35">
+      <c r="D34">
         <f>SUBTOTAL(109,[flash])</f>
         <v>0</v>
       </c>
-      <c r="E35">
+      <c r="E34">
         <f>SUBTOTAL(109,[Code])</f>
         <v>0</v>
       </c>
-      <c r="F35">
+      <c r="F34">
         <f>SUBTOTAL(109,[RO_data])</f>
         <v>0</v>
       </c>
-      <c r="G35">
+      <c r="G34">
         <f>SUBTOTAL(109,[RW_data])</f>
         <v>0</v>
       </c>
-      <c r="H35">
+      <c r="H34">
         <f>SUBTOTAL(109,[ZI_data])</f>
         <v>0</v>
       </c>
@@ -1411,7 +1402,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H35"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="16.7109375" customWidth="1"/>
@@ -1424,28 +1415,28 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E2" t="s">
         <v>37</v>
       </c>
-      <c r="D2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>38</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>39</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>40</v>
-      </c>
-      <c r="H2" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1453,16 +1444,16 @@
         <v>4</v>
       </c>
       <c r="B3" s="2">
-        <v>22.00537872314453</v>
+        <v>24.98612403869629</v>
       </c>
       <c r="C3" s="1">
-        <v>3191</v>
+        <v>3151</v>
       </c>
       <c r="D3" s="1">
         <v>800</v>
       </c>
       <c r="E3" s="1">
-        <v>3148</v>
+        <v>3108</v>
       </c>
       <c r="F3" s="1">
         <v>43</v>
@@ -1479,16 +1470,16 @@
         <v>5</v>
       </c>
       <c r="B4" s="2">
-        <v>13.32321929931641</v>
+        <v>8.104036331176758</v>
       </c>
       <c r="C4" s="1">
-        <v>1932</v>
+        <v>1022</v>
       </c>
       <c r="D4" s="1">
         <v>64</v>
       </c>
       <c r="E4" s="1">
-        <v>1912</v>
+        <v>1002</v>
       </c>
       <c r="F4" s="1">
         <v>20</v>
@@ -1505,16 +1496,16 @@
         <v>6</v>
       </c>
       <c r="B5" s="2">
-        <v>8.337355613708496</v>
+        <v>7.44588041305542</v>
       </c>
       <c r="C5" s="1">
-        <v>1209</v>
+        <v>939</v>
       </c>
       <c r="D5" s="1">
         <v>60</v>
       </c>
       <c r="E5" s="1">
-        <v>1188</v>
+        <v>918</v>
       </c>
       <c r="F5" s="1">
         <v>21</v>
@@ -1531,16 +1522,16 @@
         <v>8</v>
       </c>
       <c r="B6" s="2">
-        <v>7.12364673614502</v>
+        <v>7.271429538726807</v>
       </c>
       <c r="C6" s="1">
-        <v>1033</v>
+        <v>917</v>
       </c>
       <c r="D6" s="1">
         <v>9</v>
       </c>
       <c r="E6" s="1">
-        <v>988</v>
+        <v>872</v>
       </c>
       <c r="F6" s="1">
         <v>41</v>
@@ -1554,97 +1545,97 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B7" s="2">
-        <v>5.047927856445313</v>
+        <v>5.756878852844238</v>
       </c>
       <c r="C7" s="1">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="D7" s="1">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="E7" s="1">
-        <v>732</v>
+        <v>722</v>
       </c>
       <c r="F7" s="1">
         <v>0</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H7" s="1">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="1" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B8" s="2">
-        <v>5.006551265716553</v>
+        <v>5.265244483947754</v>
       </c>
       <c r="C8" s="1">
-        <v>726</v>
+        <v>664</v>
       </c>
       <c r="D8" s="1">
-        <v>4</v>
+        <v>76828</v>
       </c>
       <c r="E8" s="1">
-        <v>722</v>
+        <v>626</v>
       </c>
       <c r="F8" s="1">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="G8" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H8" s="1">
-        <v>0</v>
+        <v>76828</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="1" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="B9" s="2">
-        <v>4.578994750976563</v>
+        <v>4.694314479827881</v>
       </c>
       <c r="C9" s="1">
-        <v>664</v>
+        <v>592</v>
       </c>
       <c r="D9" s="1">
-        <v>76828</v>
+        <v>0</v>
       </c>
       <c r="E9" s="1">
-        <v>626</v>
+        <v>592</v>
       </c>
       <c r="F9" s="1">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="G9" s="1">
         <v>0</v>
       </c>
       <c r="H9" s="1">
-        <v>76828</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="1" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="B10" s="2">
-        <v>4.08247709274292</v>
+        <v>4.472286224365234</v>
       </c>
       <c r="C10" s="1">
-        <v>592</v>
+        <v>564</v>
       </c>
       <c r="D10" s="1">
-        <v>0</v>
+        <v>1028</v>
       </c>
       <c r="E10" s="1">
-        <v>592</v>
+        <v>564</v>
       </c>
       <c r="F10" s="1">
         <v>0</v>
@@ -1653,56 +1644,56 @@
         <v>0</v>
       </c>
       <c r="H10" s="1">
-        <v>0</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="1" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="B11" s="2">
-        <v>3.889386892318726</v>
+        <v>4.234398365020752</v>
       </c>
       <c r="C11" s="1">
-        <v>564</v>
+        <v>534</v>
       </c>
       <c r="D11" s="1">
-        <v>1028</v>
+        <v>4</v>
       </c>
       <c r="E11" s="1">
-        <v>564</v>
+        <v>530</v>
       </c>
       <c r="F11" s="1">
         <v>0</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H11" s="1">
-        <v>1028</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B12" s="2">
-        <v>3.682504653930664</v>
+        <v>3.742764234542847</v>
       </c>
       <c r="C12" s="1">
-        <v>534</v>
+        <v>472</v>
       </c>
       <c r="D12" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E12" s="1">
-        <v>530</v>
+        <v>472</v>
       </c>
       <c r="F12" s="1">
         <v>0</v>
       </c>
       <c r="G12" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H12" s="1">
         <v>0</v>
@@ -1710,19 +1701,19 @@
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B13" s="2">
-        <v>3.254947900772095</v>
+        <v>3.726905107498169</v>
       </c>
       <c r="C13" s="1">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="D13" s="1">
         <v>0</v>
       </c>
       <c r="E13" s="1">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="F13" s="1">
         <v>0</v>
@@ -1736,19 +1727,19 @@
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B14" s="2">
-        <v>3.241155862808228</v>
+        <v>3.441440105438232</v>
       </c>
       <c r="C14" s="1">
-        <v>470</v>
+        <v>434</v>
       </c>
       <c r="D14" s="1">
         <v>0</v>
       </c>
       <c r="E14" s="1">
-        <v>470</v>
+        <v>434</v>
       </c>
       <c r="F14" s="1">
         <v>0</v>
@@ -1762,54 +1753,54 @@
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="1" t="s">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="B15" s="2">
-        <v>2.992897033691406</v>
+        <v>3.39386248588562</v>
       </c>
       <c r="C15" s="1">
-        <v>434</v>
+        <v>428</v>
       </c>
       <c r="D15" s="1">
-        <v>0</v>
+        <v>1024</v>
       </c>
       <c r="E15" s="1">
-        <v>434</v>
+        <v>36</v>
       </c>
       <c r="F15" s="1">
-        <v>0</v>
+        <v>392</v>
       </c>
       <c r="G15" s="1">
         <v>0</v>
       </c>
       <c r="H15" s="1">
-        <v>0</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="1" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B16" s="2">
-        <v>2.951520681381226</v>
+        <v>2.410593986511231</v>
       </c>
       <c r="C16" s="1">
-        <v>428</v>
+        <v>304</v>
       </c>
       <c r="D16" s="1">
-        <v>1024</v>
+        <v>12</v>
       </c>
       <c r="E16" s="1">
-        <v>36</v>
+        <v>304</v>
       </c>
       <c r="F16" s="1">
-        <v>392</v>
+        <v>0</v>
       </c>
       <c r="G16" s="1">
         <v>0</v>
       </c>
       <c r="H16" s="1">
-        <v>1024</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -1817,7 +1808,7 @@
         <v>17</v>
       </c>
       <c r="B17" s="2">
-        <v>1.986069917678833</v>
+        <v>2.28372049331665</v>
       </c>
       <c r="C17" s="1">
         <v>288</v>
@@ -1843,7 +1834,7 @@
         <v>18</v>
       </c>
       <c r="B18" s="2">
-        <v>1.889524817466736</v>
+        <v>2.172706365585327</v>
       </c>
       <c r="C18" s="1">
         <v>274</v>
@@ -1869,16 +1860,16 @@
         <v>12</v>
       </c>
       <c r="B19" s="2">
-        <v>1.627473950386047</v>
+        <v>1.63349461555481</v>
       </c>
       <c r="C19" s="1">
-        <v>236</v>
+        <v>206</v>
       </c>
       <c r="D19" s="1">
         <v>4</v>
       </c>
       <c r="E19" s="1">
-        <v>232</v>
+        <v>202</v>
       </c>
       <c r="F19" s="1">
         <v>0</v>
@@ -1895,7 +1886,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="2">
-        <v>1.241293668746948</v>
+        <v>1.427325367927551</v>
       </c>
       <c r="C20" s="1">
         <v>180</v>
@@ -1921,7 +1912,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="2">
-        <v>1.034411430358887</v>
+        <v>1.189437747001648</v>
       </c>
       <c r="C21" s="1">
         <v>150</v>
@@ -1947,16 +1938,16 @@
         <v>21</v>
       </c>
       <c r="B22" s="2">
-        <v>0.6620233058929443</v>
+        <v>0.3806200921535492</v>
       </c>
       <c r="C22" s="1">
-        <v>96</v>
+        <v>48</v>
       </c>
       <c r="D22" s="1">
         <v>0</v>
       </c>
       <c r="E22" s="1">
-        <v>96</v>
+        <v>48</v>
       </c>
       <c r="F22" s="1">
         <v>0</v>
@@ -1973,16 +1964,16 @@
         <v>22</v>
       </c>
       <c r="B23" s="2">
-        <v>0.3310116529464722</v>
+        <v>0.3489017486572266</v>
       </c>
       <c r="C23" s="1">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D23" s="1">
         <v>0</v>
       </c>
       <c r="E23" s="1">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F23" s="1">
         <v>0</v>
@@ -1999,16 +1990,16 @@
         <v>23</v>
       </c>
       <c r="B24" s="2">
-        <v>0.3034273386001587</v>
+        <v>0.2854650616645813</v>
       </c>
       <c r="C24" s="1">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="D24" s="1">
         <v>0</v>
       </c>
       <c r="E24" s="1">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="F24" s="1">
         <v>0</v>
@@ -2025,7 +2016,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="2">
-        <v>0.2482587397098541</v>
+        <v>0.2854650616645813</v>
       </c>
       <c r="C25" s="1">
         <v>36</v>
@@ -2051,7 +2042,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="2">
-        <v>0.2482587397098541</v>
+        <v>0.2854650616645813</v>
       </c>
       <c r="C26" s="1">
         <v>36</v>
@@ -2077,16 +2068,16 @@
         <v>26</v>
       </c>
       <c r="B27" s="2">
-        <v>0.2482587397098541</v>
+        <v>0.2378875613212585</v>
       </c>
       <c r="C27" s="1">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D27" s="1">
         <v>0</v>
       </c>
       <c r="E27" s="1">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F27" s="1">
         <v>0</v>
@@ -2103,7 +2094,7 @@
         <v>27</v>
       </c>
       <c r="B28" s="2">
-        <v>0.2068822830915451</v>
+        <v>0.2378875613212585</v>
       </c>
       <c r="C28" s="1">
         <v>30</v>
@@ -2129,16 +2120,16 @@
         <v>28</v>
       </c>
       <c r="B29" s="2">
-        <v>0.2068822830915451</v>
+        <v>0.0951550230383873</v>
       </c>
       <c r="C29" s="1">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="D29" s="1">
         <v>0</v>
       </c>
       <c r="E29" s="1">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="F29" s="1">
         <v>0</v>
@@ -2155,16 +2146,16 @@
         <v>29</v>
       </c>
       <c r="B30" s="2">
-        <v>0.08275291323661804</v>
+        <v>0.06343667954206467</v>
       </c>
       <c r="C30" s="1">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D30" s="1">
         <v>0</v>
       </c>
       <c r="E30" s="1">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F30" s="1">
         <v>0</v>
@@ -2181,7 +2172,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="2">
-        <v>0.05516861006617546</v>
+        <v>0.06343667954206467</v>
       </c>
       <c r="C31" s="1">
         <v>8</v>
@@ -2204,25 +2195,25 @@
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="1" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="B32" s="2">
-        <v>0.05516861006617546</v>
+        <v>0.03171833977103233</v>
       </c>
       <c r="C32" s="1">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D32" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E32" s="1">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F32" s="1">
         <v>0</v>
       </c>
       <c r="G32" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H32" s="1">
         <v>0</v>
@@ -2230,85 +2221,59 @@
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="1" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="B33" s="2">
-        <v>0.02758430503308773</v>
+        <v>0.03171833977103233</v>
       </c>
       <c r="C33" s="1">
         <v>4</v>
       </c>
       <c r="D33" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E33" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F33" s="1">
         <v>0</v>
       </c>
       <c r="G33" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H33" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:8">
-      <c r="A34" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B34" s="2">
-        <v>0.02758430503308773</v>
-      </c>
-      <c r="C34" s="1">
-        <v>4</v>
-      </c>
-      <c r="D34" s="1">
-        <v>0</v>
-      </c>
-      <c r="E34" s="1">
-        <v>4</v>
-      </c>
-      <c r="F34" s="1">
-        <v>0</v>
-      </c>
-      <c r="G34" s="1">
-        <v>0</v>
-      </c>
-      <c r="H34" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8">
-      <c r="A35" t="s">
-        <v>34</v>
-      </c>
-      <c r="B35">
+      <c r="A34" t="s">
+        <v>33</v>
+      </c>
+      <c r="B34">
         <f>SUBTOTAL(109,[flash_percent])</f>
         <v>0</v>
       </c>
-      <c r="C35">
+      <c r="C34">
         <f>SUBTOTAL(109,[flash])</f>
         <v>0</v>
       </c>
-      <c r="D35">
+      <c r="D34">
         <f>SUBTOTAL(109,[ram])</f>
         <v>0</v>
       </c>
-      <c r="E35">
+      <c r="E34">
         <f>SUBTOTAL(109,[Code])</f>
         <v>0</v>
       </c>
-      <c r="F35">
+      <c r="F34">
         <f>SUBTOTAL(109,[RO_data])</f>
         <v>0</v>
       </c>
-      <c r="G35">
+      <c r="G34">
         <f>SUBTOTAL(109,[RW_data])</f>
         <v>0</v>
       </c>
-      <c r="H35">
+      <c r="H34">
         <f>SUBTOTAL(109,[ZI_data])</f>
         <v>0</v>
       </c>

--- a/03_GD32F407_FreeRTOS_BinarySemaphore/Project/GD32F407_analysis.xlsx
+++ b/03_GD32F407_FreeRTOS_BinarySemaphore/Project/GD32F407_analysis.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="43">
   <si>
     <t>GD32F407</t>
   </si>
@@ -53,13 +53,10 @@
     <t>system_gd32f4xx.o</t>
   </si>
   <si>
-    <t>bsp_keys.o</t>
-  </si>
-  <si>
     <t>gd32f4xx_usart.o</t>
   </si>
   <si>
-    <t>printf3.o</t>
+    <t>printf4.o</t>
   </si>
   <si>
     <t>exti.o</t>
@@ -80,12 +77,12 @@
     <t>list.o</t>
   </si>
   <si>
+    <t>uldiv.o</t>
+  </si>
+  <si>
     <t>init.o</t>
   </si>
   <si>
-    <t>uidiv.o</t>
-  </si>
-  <si>
     <t>puts.o</t>
   </si>
   <si>
@@ -93,6 +90,12 @@
   </si>
   <si>
     <t>memcpya.o</t>
+  </si>
+  <si>
+    <t>llushr.o</t>
+  </si>
+  <si>
+    <t>llshl.o</t>
   </si>
   <si>
     <t>handlers.o</t>
@@ -230,9 +233,9 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>ram_percent!$A$3:$A$34</c:f>
+              <c:f>ram_percent!$A$3:$A$35</c:f>
               <c:strCache>
-                <c:ptCount val="32"/>
+                <c:ptCount val="33"/>
                 <c:pt idx="0">
                   <c:v>heap_4.o</c:v>
                 </c:pt>
@@ -266,10 +269,7 @@
                 <c:pt idx="10">
                   <c:v>system_gd32f4xx.o</c:v>
                 </c:pt>
-                <c:pt idx="11">
-                  <c:v>bsp_keys.o</c:v>
-                </c:pt>
-                <c:pt idx="31">
+                <c:pt idx="32">
                   <c:v>Totals</c:v>
                 </c:pt>
               </c:strCache>
@@ -277,10 +277,10 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>ram_percent!$B$3:$B$34</c:f>
+              <c:f>ram_percent!$B$3:$B$35</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="32"/>
+                <c:ptCount val="33"/>
                 <c:pt idx="0">
                   <c:v>96.22624969482422</c:v>
                 </c:pt>
@@ -300,7 +300,7 @@
                   <c:v>0.07514935731887817</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.01502987183630467</c:v>
+                  <c:v>0.02003982849419117</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>0.01127240434288979</c:v>
@@ -314,10 +314,7 @@
                 <c:pt idx="10">
                   <c:v>0.005009957123547792</c:v>
                 </c:pt>
-                <c:pt idx="11">
-                  <c:v>0.005009957123547792</c:v>
-                </c:pt>
-                <c:pt idx="31">
+                <c:pt idx="32">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -385,9 +382,9 @@
           </c:tx>
           <c:cat>
             <c:strRef>
-              <c:f>flash_percent!$A$3:$A$34</c:f>
+              <c:f>flash_percent!$A$3:$A$35</c:f>
               <c:strCache>
-                <c:ptCount val="32"/>
+                <c:ptCount val="33"/>
                 <c:pt idx="0">
                   <c:v>tasks.o</c:v>
                 </c:pt>
@@ -395,40 +392,40 @@
                   <c:v>queue.o</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>port.o</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>mc_w.l</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>timers.o</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>port.o</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>mc_w.l</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>heap_4.o</c:v>
                 </c:pt>
                 <c:pt idx="6">
+                  <c:v>main.o</c:v>
+                </c:pt>
+                <c:pt idx="7">
                   <c:v>gd32f4xx_usart.o</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="8">
+                  <c:v>printf4.o</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>usart0.o</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="10">
                   <c:v>system_gd32f4xx.o</c:v>
                 </c:pt>
-                <c:pt idx="9">
-                  <c:v>printf3.o</c:v>
-                </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="11">
                   <c:v>exti.o</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="12">
                   <c:v>gd32f4xx_dma.o</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="13">
                   <c:v>startup_gd32f407_427.o</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>main.o</c:v>
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>gd32f4xx_rcu.o</c:v>
@@ -437,51 +434,54 @@
                   <c:v>gd32f4xx_gpio.o</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>bsp_keys.o</c:v>
+                  <c:v>gd32f4xx_misc.o</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>gd32f4xx_misc.o</c:v>
+                  <c:v>list.o</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>list.o</c:v>
+                  <c:v>uldiv.o</c:v>
                 </c:pt>
                 <c:pt idx="19">
                   <c:v>init.o</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>uidiv.o</c:v>
+                  <c:v>puts.o</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>puts.o</c:v>
+                  <c:v>memseta.o</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>memseta.o</c:v>
+                  <c:v>memcpya.o</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>memcpya.o</c:v>
+                  <c:v>llushr.o</c:v>
                 </c:pt>
                 <c:pt idx="24">
+                  <c:v>llshl.o</c:v>
+                </c:pt>
+                <c:pt idx="25">
                   <c:v>handlers.o</c:v>
                 </c:pt>
-                <c:pt idx="25">
+                <c:pt idx="26">
                   <c:v>gd32f4xx_exti.o</c:v>
                 </c:pt>
-                <c:pt idx="26">
+                <c:pt idx="27">
                   <c:v>gd32f4xx_it.o</c:v>
                 </c:pt>
-                <c:pt idx="27">
+                <c:pt idx="28">
                   <c:v>entry9a.o</c:v>
                 </c:pt>
-                <c:pt idx="28">
+                <c:pt idx="29">
                   <c:v>entry2.o</c:v>
                 </c:pt>
-                <c:pt idx="29">
+                <c:pt idx="30">
                   <c:v>stdout.o</c:v>
                 </c:pt>
-                <c:pt idx="30">
+                <c:pt idx="31">
                   <c:v>entry5.o</c:v>
                 </c:pt>
-                <c:pt idx="31">
+                <c:pt idx="32">
                   <c:v>Totals</c:v>
                 </c:pt>
               </c:strCache>
@@ -489,104 +489,107 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>flash_percent!$B$3:$B$34</c:f>
+              <c:f>flash_percent!$B$3:$B$35</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="32"/>
+                <c:ptCount val="33"/>
                 <c:pt idx="0">
-                  <c:v>24.98612403869629</c:v>
+                  <c:v>25.07060813903809</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>8.104036331176758</c:v>
+                  <c:v>14.97536945343018</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>7.44588041305542</c:v>
+                  <c:v>6.784893035888672</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>7.271429538726807</c:v>
+                  <c:v>6.292282581329346</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5.756878852844238</c:v>
+                  <c:v>6.167487621307373</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>5.265244483947754</c:v>
+                  <c:v>4.361248016357422</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>4.694314479827881</c:v>
+                  <c:v>4.072249412536621</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>4.472286224365234</c:v>
+                  <c:v>3.888341426849365</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>4.234398365020752</c:v>
+                  <c:v>3.862068891525269</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>3.742764234542847</c:v>
+                  <c:v>3.704433441162109</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>3.726905107498169</c:v>
+                  <c:v>3.507389068603516</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>3.441440105438232</c:v>
+                  <c:v>3.087028026580811</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>3.39386248588562</c:v>
+                  <c:v>2.850574731826782</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2.410593986511231</c:v>
+                  <c:v>2.811165809631348</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2.28372049331665</c:v>
+                  <c:v>1.891625642776489</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>2.172706365585327</c:v>
+                  <c:v>1.799671649932861</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.63349461555481</c:v>
+                  <c:v>1.182265996932983</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.427325367927551</c:v>
+                  <c:v>0.9852216839790344</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1.189437747001648</c:v>
+                  <c:v>0.6436781883239746</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.3806200921535492</c:v>
+                  <c:v>0.3152709305286408</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.3489017486572266</c:v>
+                  <c:v>0.2364532053470612</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.2854650616645813</c:v>
+                  <c:v>0.2364532053470612</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.2854650616645813</c:v>
+                  <c:v>0.2364532053470612</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.2854650616645813</c:v>
+                  <c:v>0.2101806253194809</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.2378875613212585</c:v>
+                  <c:v>0.1970443278551102</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.2378875613212585</c:v>
+                  <c:v>0.1970443278551102</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.0951550230383873</c:v>
+                  <c:v>0.1970443278551102</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.06343667954206467</c:v>
+                  <c:v>0.07881773263216019</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.06343667954206467</c:v>
+                  <c:v>0.05254515632987022</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.03171833977103233</c:v>
+                  <c:v>0.05254515632987022</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.03171833977103233</c:v>
+                  <c:v>0.02627257816493511</c:v>
                 </c:pt>
                 <c:pt idx="31">
+                  <c:v>0.02627257816493511</c:v>
+                </c:pt>
+                <c:pt idx="32">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -691,8 +694,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A2:H34" totalsRowCount="1">
-  <autoFilter ref="A2:H33"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A2:H35" totalsRowCount="1">
+  <autoFilter ref="A2:H34"/>
   <tableColumns count="8">
     <tableColumn id="1" name="File_name" totalsRowLabel="Totals"/>
     <tableColumn id="2" name="ram_percent" totalsRowFunction="sum"/>
@@ -708,8 +711,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A2:H34" totalsRowCount="1">
-  <autoFilter ref="A2:H33"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A2:H35" totalsRowCount="1">
+  <autoFilter ref="A2:H34"/>
   <tableColumns count="8">
     <tableColumn id="1" name="File_name" totalsRowLabel="Totals"/>
     <tableColumn id="2" name="flash_percent" totalsRowFunction="sum"/>
@@ -1009,7 +1012,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H34"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="16.7109375" customWidth="1"/>
@@ -1022,28 +1025,28 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1135,10 +1138,10 @@
         <v>800</v>
       </c>
       <c r="D6" s="1">
-        <v>3151</v>
+        <v>3817</v>
       </c>
       <c r="E6" s="1">
-        <v>3108</v>
+        <v>3774</v>
       </c>
       <c r="F6" s="1">
         <v>43</v>
@@ -1161,10 +1164,10 @@
         <v>64</v>
       </c>
       <c r="D7" s="1">
-        <v>1022</v>
+        <v>2280</v>
       </c>
       <c r="E7" s="1">
-        <v>1002</v>
+        <v>2260</v>
       </c>
       <c r="F7" s="1">
         <v>20</v>
@@ -1207,16 +1210,16 @@
         <v>7</v>
       </c>
       <c r="B9" s="2">
-        <v>0.01502987183630467</v>
+        <v>0.02003982849419117</v>
       </c>
       <c r="C9" s="1">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D9" s="1">
-        <v>304</v>
+        <v>620</v>
       </c>
       <c r="E9" s="1">
-        <v>304</v>
+        <v>620</v>
       </c>
       <c r="F9" s="1">
         <v>0</v>
@@ -1225,7 +1228,7 @@
         <v>0</v>
       </c>
       <c r="H9" s="1">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1239,10 +1242,10 @@
         <v>9</v>
       </c>
       <c r="D10" s="1">
-        <v>917</v>
+        <v>1033</v>
       </c>
       <c r="E10" s="1">
-        <v>872</v>
+        <v>988</v>
       </c>
       <c r="F10" s="1">
         <v>41</v>
@@ -1265,10 +1268,10 @@
         <v>4</v>
       </c>
       <c r="D11" s="1">
-        <v>726</v>
+        <v>958</v>
       </c>
       <c r="E11" s="1">
-        <v>722</v>
+        <v>954</v>
       </c>
       <c r="F11" s="1">
         <v>0</v>
@@ -1332,61 +1335,35 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
-      <c r="A14" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B14" s="2">
-        <v>0.005009957123547792</v>
-      </c>
-      <c r="C14" s="1">
-        <v>4</v>
-      </c>
-      <c r="D14" s="1">
-        <v>206</v>
-      </c>
-      <c r="E14" s="1">
-        <v>202</v>
-      </c>
-      <c r="F14" s="1">
-        <v>0</v>
-      </c>
-      <c r="G14" s="1">
-        <v>4</v>
-      </c>
-      <c r="H14" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8">
-      <c r="A34" t="s">
-        <v>33</v>
-      </c>
-      <c r="B34">
+    <row r="35" spans="1:8">
+      <c r="A35" t="s">
+        <v>34</v>
+      </c>
+      <c r="B35">
         <f>SUBTOTAL(109,[ram_percent])</f>
         <v>0</v>
       </c>
-      <c r="C34">
+      <c r="C35">
         <f>SUBTOTAL(109,[ram])</f>
         <v>0</v>
       </c>
-      <c r="D34">
+      <c r="D35">
         <f>SUBTOTAL(109,[flash])</f>
         <v>0</v>
       </c>
-      <c r="E34">
+      <c r="E35">
         <f>SUBTOTAL(109,[Code])</f>
         <v>0</v>
       </c>
-      <c r="F34">
+      <c r="F35">
         <f>SUBTOTAL(109,[RO_data])</f>
         <v>0</v>
       </c>
-      <c r="G34">
+      <c r="G35">
         <f>SUBTOTAL(109,[RW_data])</f>
         <v>0</v>
       </c>
-      <c r="H34">
+      <c r="H35">
         <f>SUBTOTAL(109,[ZI_data])</f>
         <v>0</v>
       </c>
@@ -1402,7 +1379,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H34"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="8" width="16.7109375" customWidth="1"/>
@@ -1415,28 +1392,28 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H2" t="s">
         <v>41</v>
-      </c>
-      <c r="C2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E2" t="s">
-        <v>37</v>
-      </c>
-      <c r="F2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G2" t="s">
-        <v>39</v>
-      </c>
-      <c r="H2" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1444,16 +1421,16 @@
         <v>4</v>
       </c>
       <c r="B3" s="2">
-        <v>24.98612403869629</v>
+        <v>25.07060813903809</v>
       </c>
       <c r="C3" s="1">
-        <v>3151</v>
+        <v>3817</v>
       </c>
       <c r="D3" s="1">
         <v>800</v>
       </c>
       <c r="E3" s="1">
-        <v>3108</v>
+        <v>3774</v>
       </c>
       <c r="F3" s="1">
         <v>43</v>
@@ -1470,16 +1447,16 @@
         <v>5</v>
       </c>
       <c r="B4" s="2">
-        <v>8.104036331176758</v>
+        <v>14.97536945343018</v>
       </c>
       <c r="C4" s="1">
-        <v>1022</v>
+        <v>2280</v>
       </c>
       <c r="D4" s="1">
         <v>64</v>
       </c>
       <c r="E4" s="1">
-        <v>1002</v>
+        <v>2260</v>
       </c>
       <c r="F4" s="1">
         <v>20</v>
@@ -1493,80 +1470,80 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B5" s="2">
-        <v>7.44588041305542</v>
+        <v>6.784893035888672</v>
       </c>
       <c r="C5" s="1">
-        <v>939</v>
+        <v>1033</v>
       </c>
       <c r="D5" s="1">
-        <v>60</v>
+        <v>9</v>
       </c>
       <c r="E5" s="1">
-        <v>918</v>
+        <v>988</v>
       </c>
       <c r="F5" s="1">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H5" s="1">
-        <v>60</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B6" s="2">
-        <v>7.271429538726807</v>
+        <v>6.292282581329346</v>
       </c>
       <c r="C6" s="1">
-        <v>917</v>
+        <v>958</v>
       </c>
       <c r="D6" s="1">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E6" s="1">
-        <v>872</v>
+        <v>954</v>
       </c>
       <c r="F6" s="1">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="G6" s="1">
         <v>4</v>
       </c>
       <c r="H6" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B7" s="2">
-        <v>5.756878852844238</v>
+        <v>6.167487621307373</v>
       </c>
       <c r="C7" s="1">
-        <v>726</v>
+        <v>939</v>
       </c>
       <c r="D7" s="1">
-        <v>4</v>
+        <v>60</v>
       </c>
       <c r="E7" s="1">
-        <v>722</v>
+        <v>918</v>
       </c>
       <c r="F7" s="1">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G7" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H7" s="1">
-        <v>0</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1574,7 +1551,7 @@
         <v>1</v>
       </c>
       <c r="B8" s="2">
-        <v>5.265244483947754</v>
+        <v>4.361248016357422</v>
       </c>
       <c r="C8" s="1">
         <v>664</v>
@@ -1597,19 +1574,19 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="1" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B9" s="2">
-        <v>4.694314479827881</v>
+        <v>4.072249412536621</v>
       </c>
       <c r="C9" s="1">
-        <v>592</v>
+        <v>620</v>
       </c>
       <c r="D9" s="1">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="E9" s="1">
-        <v>592</v>
+        <v>620</v>
       </c>
       <c r="F9" s="1">
         <v>0</v>
@@ -1618,24 +1595,24 @@
         <v>0</v>
       </c>
       <c r="H9" s="1">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="1" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="B10" s="2">
-        <v>4.472286224365234</v>
+        <v>3.888341426849365</v>
       </c>
       <c r="C10" s="1">
-        <v>564</v>
+        <v>592</v>
       </c>
       <c r="D10" s="1">
-        <v>1028</v>
+        <v>0</v>
       </c>
       <c r="E10" s="1">
-        <v>564</v>
+        <v>592</v>
       </c>
       <c r="F10" s="1">
         <v>0</v>
@@ -1644,30 +1621,30 @@
         <v>0</v>
       </c>
       <c r="H10" s="1">
-        <v>1028</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B11" s="2">
-        <v>4.234398365020752</v>
+        <v>3.862068891525269</v>
       </c>
       <c r="C11" s="1">
-        <v>534</v>
+        <v>588</v>
       </c>
       <c r="D11" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E11" s="1">
-        <v>530</v>
+        <v>588</v>
       </c>
       <c r="F11" s="1">
         <v>0</v>
       </c>
       <c r="G11" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H11" s="1">
         <v>0</v>
@@ -1675,19 +1652,19 @@
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="1" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B12" s="2">
-        <v>3.742764234542847</v>
+        <v>3.704433441162109</v>
       </c>
       <c r="C12" s="1">
-        <v>472</v>
+        <v>564</v>
       </c>
       <c r="D12" s="1">
-        <v>0</v>
+        <v>1028</v>
       </c>
       <c r="E12" s="1">
-        <v>472</v>
+        <v>564</v>
       </c>
       <c r="F12" s="1">
         <v>0</v>
@@ -1696,30 +1673,30 @@
         <v>0</v>
       </c>
       <c r="H12" s="1">
-        <v>0</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B13" s="2">
-        <v>3.726905107498169</v>
+        <v>3.507389068603516</v>
       </c>
       <c r="C13" s="1">
-        <v>470</v>
+        <v>534</v>
       </c>
       <c r="D13" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E13" s="1">
-        <v>470</v>
+        <v>530</v>
       </c>
       <c r="F13" s="1">
         <v>0</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H13" s="1">
         <v>0</v>
@@ -1727,19 +1704,19 @@
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B14" s="2">
-        <v>3.441440105438232</v>
+        <v>3.087028026580811</v>
       </c>
       <c r="C14" s="1">
-        <v>434</v>
+        <v>470</v>
       </c>
       <c r="D14" s="1">
         <v>0</v>
       </c>
       <c r="E14" s="1">
-        <v>434</v>
+        <v>470</v>
       </c>
       <c r="F14" s="1">
         <v>0</v>
@@ -1753,62 +1730,62 @@
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="1" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="B15" s="2">
-        <v>3.39386248588562</v>
+        <v>2.850574731826782</v>
       </c>
       <c r="C15" s="1">
-        <v>428</v>
+        <v>434</v>
       </c>
       <c r="D15" s="1">
-        <v>1024</v>
+        <v>0</v>
       </c>
       <c r="E15" s="1">
-        <v>36</v>
+        <v>434</v>
       </c>
       <c r="F15" s="1">
-        <v>392</v>
+        <v>0</v>
       </c>
       <c r="G15" s="1">
         <v>0</v>
       </c>
       <c r="H15" s="1">
-        <v>1024</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B16" s="2">
-        <v>2.410593986511231</v>
+        <v>2.811165809631348</v>
       </c>
       <c r="C16" s="1">
-        <v>304</v>
+        <v>428</v>
       </c>
       <c r="D16" s="1">
-        <v>12</v>
+        <v>1024</v>
       </c>
       <c r="E16" s="1">
-        <v>304</v>
+        <v>36</v>
       </c>
       <c r="F16" s="1">
-        <v>0</v>
+        <v>392</v>
       </c>
       <c r="G16" s="1">
         <v>0</v>
       </c>
       <c r="H16" s="1">
-        <v>12</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B17" s="2">
-        <v>2.28372049331665</v>
+        <v>1.891625642776489</v>
       </c>
       <c r="C17" s="1">
         <v>288</v>
@@ -1831,10 +1808,10 @@
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B18" s="2">
-        <v>2.172706365585327</v>
+        <v>1.799671649932861</v>
       </c>
       <c r="C18" s="1">
         <v>274</v>
@@ -1857,25 +1834,25 @@
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="B19" s="2">
-        <v>1.63349461555481</v>
+        <v>1.182265996932983</v>
       </c>
       <c r="C19" s="1">
-        <v>206</v>
+        <v>180</v>
       </c>
       <c r="D19" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E19" s="1">
-        <v>202</v>
+        <v>180</v>
       </c>
       <c r="F19" s="1">
         <v>0</v>
       </c>
       <c r="G19" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H19" s="1">
         <v>0</v>
@@ -1886,16 +1863,16 @@
         <v>19</v>
       </c>
       <c r="B20" s="2">
-        <v>1.427325367927551</v>
+        <v>0.9852216839790344</v>
       </c>
       <c r="C20" s="1">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="D20" s="1">
         <v>0</v>
       </c>
       <c r="E20" s="1">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="F20" s="1">
         <v>0</v>
@@ -1912,16 +1889,16 @@
         <v>20</v>
       </c>
       <c r="B21" s="2">
-        <v>1.189437747001648</v>
+        <v>0.6436781883239746</v>
       </c>
       <c r="C21" s="1">
-        <v>150</v>
+        <v>98</v>
       </c>
       <c r="D21" s="1">
         <v>0</v>
       </c>
       <c r="E21" s="1">
-        <v>150</v>
+        <v>98</v>
       </c>
       <c r="F21" s="1">
         <v>0</v>
@@ -1938,7 +1915,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="2">
-        <v>0.3806200921535492</v>
+        <v>0.3152709305286408</v>
       </c>
       <c r="C22" s="1">
         <v>48</v>
@@ -1964,16 +1941,16 @@
         <v>22</v>
       </c>
       <c r="B23" s="2">
-        <v>0.3489017486572266</v>
+        <v>0.2364532053470612</v>
       </c>
       <c r="C23" s="1">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="D23" s="1">
         <v>0</v>
       </c>
       <c r="E23" s="1">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="F23" s="1">
         <v>0</v>
@@ -1990,7 +1967,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="2">
-        <v>0.2854650616645813</v>
+        <v>0.2364532053470612</v>
       </c>
       <c r="C24" s="1">
         <v>36</v>
@@ -2016,7 +1993,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="2">
-        <v>0.2854650616645813</v>
+        <v>0.2364532053470612</v>
       </c>
       <c r="C25" s="1">
         <v>36</v>
@@ -2042,16 +2019,16 @@
         <v>25</v>
       </c>
       <c r="B26" s="2">
-        <v>0.2854650616645813</v>
+        <v>0.2101806253194809</v>
       </c>
       <c r="C26" s="1">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D26" s="1">
         <v>0</v>
       </c>
       <c r="E26" s="1">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="F26" s="1">
         <v>0</v>
@@ -2068,7 +2045,7 @@
         <v>26</v>
       </c>
       <c r="B27" s="2">
-        <v>0.2378875613212585</v>
+        <v>0.1970443278551102</v>
       </c>
       <c r="C27" s="1">
         <v>30</v>
@@ -2094,7 +2071,7 @@
         <v>27</v>
       </c>
       <c r="B28" s="2">
-        <v>0.2378875613212585</v>
+        <v>0.1970443278551102</v>
       </c>
       <c r="C28" s="1">
         <v>30</v>
@@ -2120,16 +2097,16 @@
         <v>28</v>
       </c>
       <c r="B29" s="2">
-        <v>0.0951550230383873</v>
+        <v>0.1970443278551102</v>
       </c>
       <c r="C29" s="1">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="D29" s="1">
         <v>0</v>
       </c>
       <c r="E29" s="1">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="F29" s="1">
         <v>0</v>
@@ -2146,16 +2123,16 @@
         <v>29</v>
       </c>
       <c r="B30" s="2">
-        <v>0.06343667954206467</v>
+        <v>0.07881773263216019</v>
       </c>
       <c r="C30" s="1">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D30" s="1">
         <v>0</v>
       </c>
       <c r="E30" s="1">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F30" s="1">
         <v>0</v>
@@ -2172,7 +2149,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="2">
-        <v>0.06343667954206467</v>
+        <v>0.05254515632987022</v>
       </c>
       <c r="C31" s="1">
         <v>8</v>
@@ -2195,25 +2172,25 @@
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="1" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="B32" s="2">
-        <v>0.03171833977103233</v>
+        <v>0.05254515632987022</v>
       </c>
       <c r="C32" s="1">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D32" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E32" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F32" s="1">
         <v>0</v>
       </c>
       <c r="G32" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H32" s="1">
         <v>0</v>
@@ -2221,59 +2198,85 @@
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="1" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="B33" s="2">
-        <v>0.03171833977103233</v>
+        <v>0.02627257816493511</v>
       </c>
       <c r="C33" s="1">
         <v>4</v>
       </c>
       <c r="D33" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E33" s="1">
+        <v>0</v>
+      </c>
+      <c r="F33" s="1">
+        <v>0</v>
+      </c>
+      <c r="G33" s="1">
         <v>4</v>
       </c>
-      <c r="F33" s="1">
-        <v>0</v>
-      </c>
-      <c r="G33" s="1">
-        <v>0</v>
-      </c>
       <c r="H33" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:8">
-      <c r="A34" t="s">
-        <v>33</v>
-      </c>
-      <c r="B34">
+      <c r="A34" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B34" s="2">
+        <v>0.02627257816493511</v>
+      </c>
+      <c r="C34" s="1">
+        <v>4</v>
+      </c>
+      <c r="D34" s="1">
+        <v>0</v>
+      </c>
+      <c r="E34" s="1">
+        <v>4</v>
+      </c>
+      <c r="F34" s="1">
+        <v>0</v>
+      </c>
+      <c r="G34" s="1">
+        <v>0</v>
+      </c>
+      <c r="H34" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8">
+      <c r="A35" t="s">
+        <v>34</v>
+      </c>
+      <c r="B35">
         <f>SUBTOTAL(109,[flash_percent])</f>
         <v>0</v>
       </c>
-      <c r="C34">
+      <c r="C35">
         <f>SUBTOTAL(109,[flash])</f>
         <v>0</v>
       </c>
-      <c r="D34">
+      <c r="D35">
         <f>SUBTOTAL(109,[ram])</f>
         <v>0</v>
       </c>
-      <c r="E34">
+      <c r="E35">
         <f>SUBTOTAL(109,[Code])</f>
         <v>0</v>
       </c>
-      <c r="F34">
+      <c r="F35">
         <f>SUBTOTAL(109,[RO_data])</f>
         <v>0</v>
       </c>
-      <c r="G34">
+      <c r="G35">
         <f>SUBTOTAL(109,[RW_data])</f>
         <v>0</v>
       </c>
-      <c r="H34">
+      <c r="H35">
         <f>SUBTOTAL(109,[ZI_data])</f>
         <v>0</v>
       </c>
